--- a/data/attendance/ANNEX_FORMATION_Formation_Français_-_Project_01.xlsx
+++ b/data/attendance/ANNEX_FORMATION_Formation_Français_-_Project_01.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6409B89D-4B4D-4592-B3E7-9036CEC5DBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F92DB04-C82D-4A53-B5ED-6608878ADC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="8490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Présences" sheetId="1" r:id="rId1"/>
@@ -845,40 +845,40 @@
       <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="8">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
         <v>0</v>
       </c>
       <c r="O6" s="9">
@@ -957,40 +957,40 @@
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
-      <c r="N8" s="8">
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
         <v>0</v>
       </c>
       <c r="O8" s="9">
